--- a/exports/trend_1d/HDFCBANK_full_report.xlsx
+++ b/exports/trend_1d/HDFCBANK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>6.25</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42088</v>
+        <v>42089</v>
       </c>
       <c r="H2" t="n">
-        <v>258.6</v>
+        <v>251.7</v>
       </c>
       <c r="I2" t="n">
         <v>253.3040947456369</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K2" t="n">
-        <v>4.15</v>
+        <v>1.37</v>
       </c>
       <c r="L2" t="n">
         <v>2.26</v>
@@ -555,7 +578,7 @@
         <v>0.96</v>
       </c>
       <c r="N2" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="O2" t="n">
         <v>3.03</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.49</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42143</v>
+        <v>42144</v>
       </c>
       <c r="H3" t="n">
-        <v>251.9</v>
+        <v>256</v>
       </c>
       <c r="I3" t="n">
         <v>254.5971629792891</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.08</v>
+        <v>-1.71</v>
       </c>
       <c r="L3" t="n">
         <v>5.2</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>6.66</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H4" t="n">
-        <v>265.3</v>
+        <v>254.8</v>
       </c>
       <c r="I4" t="n">
         <v>264.3719385667767</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K4" t="n">
-        <v>3.63</v>
+        <v>-0.47</v>
       </c>
       <c r="L4" t="n">
         <v>3.32</v>
@@ -669,7 +716,7 @@
         <v>1.69</v>
       </c>
       <c r="N4" t="n">
-        <v>2.63</v>
+        <v>3.96</v>
       </c>
       <c r="O4" t="n">
         <v>1.63</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.42</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42276</v>
+        <v>42277</v>
       </c>
       <c r="H5" t="n">
-        <v>266.2</v>
+        <v>267.2</v>
       </c>
       <c r="I5" t="n">
         <v>266.4848781386281</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.47</v>
+        <v>-4.87</v>
       </c>
       <c r="L5" t="n">
         <v>5.38</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.09</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42317</v>
+        <v>42318</v>
       </c>
       <c r="H6" t="n">
-        <v>266.2</v>
+        <v>263.6</v>
       </c>
       <c r="I6" t="n">
         <v>264.9597353930336</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.37</v>
+        <v>-1.35</v>
       </c>
       <c r="L6" t="n">
         <v>1.65</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>5.51</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42431</v>
+        <v>42432</v>
       </c>
       <c r="H7" t="n">
-        <v>251.8</v>
+        <v>254</v>
       </c>
       <c r="I7" t="n">
         <v>252.1562803317033</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K7" t="n">
-        <v>4.48</v>
+        <v>3.64</v>
       </c>
       <c r="L7" t="n">
         <v>5.08</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.81</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42657</v>
+        <v>42660</v>
       </c>
       <c r="H8" t="n">
-        <v>315.4</v>
+        <v>309.4</v>
       </c>
       <c r="I8" t="n">
         <v>314.9608756548208</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K8" t="n">
-        <v>24.17</v>
+        <v>21.81</v>
       </c>
       <c r="L8" t="n">
         <v>2.24</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>150</v>
+        <v>151</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>8</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>5.51</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42745</v>
+        <v>42746</v>
       </c>
       <c r="H9" t="n">
-        <v>303.6</v>
+        <v>308.5</v>
       </c>
       <c r="I9" t="n">
         <v>306.7705468237449</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K9" t="n">
-        <v>1.87</v>
+        <v>0.29</v>
       </c>
       <c r="L9" t="n">
         <v>4.14</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>4.6</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H10" t="n">
-        <v>448.1</v>
+        <v>444.1</v>
       </c>
       <c r="I10" t="n">
         <v>447.9284451306435</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K10" t="n">
-        <v>45.25</v>
+        <v>43.95</v>
       </c>
       <c r="L10" t="n">
         <v>1.49</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>176</v>
+        <v>177</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>9</v>
+      </c>
+      <c r="U10" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>4.47</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43021</v>
+        <v>43024</v>
       </c>
       <c r="H11" t="n">
-        <v>462.7</v>
+        <v>464.3</v>
       </c>
       <c r="I11" t="n">
         <v>463.3119298979738</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.19</v>
+        <v>-4.55</v>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>5.45</v>
       </c>
       <c r="M11" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="N11" t="n">
         <v>1.76</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>3.97</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43074</v>
+        <v>43075</v>
       </c>
       <c r="H12" t="n">
-        <v>455.1</v>
+        <v>450.8</v>
       </c>
       <c r="I12" t="n">
         <v>451.695939697677</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.98</v>
+        <v>-2.91</v>
       </c>
       <c r="L12" t="n">
         <v>5.36</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>3.99</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43083</v>
+        <v>43084</v>
       </c>
       <c r="H13" t="n">
-        <v>459.5</v>
+        <v>468.4</v>
       </c>
       <c r="I13" t="n">
         <v>468.1230220611268</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.93</v>
+        <v>-3.9</v>
       </c>
       <c r="L13" t="n">
-        <v>2.75</v>
+        <v>4.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0.41</v>
+        <v>0.98</v>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="O13" t="n">
         <v>-0.9399999999999999</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>4.38</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43133</v>
+        <v>43136</v>
       </c>
       <c r="H14" t="n">
-        <v>487</v>
+        <v>478.4</v>
       </c>
       <c r="I14" t="n">
         <v>479.9957269192046</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K14" t="n">
-        <v>3.97</v>
+        <v>2.13</v>
       </c>
       <c r="L14" t="n">
         <v>3.44</v>
       </c>
       <c r="M14" t="n">
-        <v>0.98</v>
+        <v>1.54</v>
       </c>
       <c r="N14" t="n">
         <v>2.17</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>5.16</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43187</v>
+        <v>43192</v>
       </c>
       <c r="H15" t="n">
-        <v>471.5</v>
+        <v>482.8</v>
       </c>
       <c r="I15" t="n">
         <v>480.3041068529096</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K15" t="n">
-        <v>1.44</v>
+        <v>-0.92</v>
       </c>
       <c r="L15" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="M15" t="n">
         <v>0.68</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.69</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43322</v>
+        <v>43325</v>
       </c>
       <c r="H16" t="n">
-        <v>528.6</v>
+        <v>522.9</v>
       </c>
       <c r="I16" t="n">
         <v>527.3526025642436</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K16" t="n">
-        <v>9.49</v>
+        <v>8.31</v>
       </c>
       <c r="L16" t="n">
         <v>3.67</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>4.57</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43426</v>
+        <v>43430</v>
       </c>
       <c r="H17" t="n">
-        <v>501.4</v>
+        <v>512.4</v>
       </c>
       <c r="I17" t="n">
         <v>505.9359468137098</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="K17" t="n">
-        <v>4.11</v>
+        <v>2.01</v>
       </c>
       <c r="L17" t="n">
         <v>0.98</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.87</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43493</v>
+        <v>43494</v>
       </c>
       <c r="H18" t="n">
-        <v>521</v>
+        <v>514.4</v>
       </c>
       <c r="I18" t="n">
         <v>516.2625021284958</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K18" t="n">
-        <v>1.68</v>
+        <v>0.39</v>
       </c>
       <c r="L18" t="n">
         <v>1.83</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>4.37</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43504</v>
+        <v>43507</v>
       </c>
       <c r="H19" t="n">
-        <v>530.6</v>
+        <v>534.9</v>
       </c>
       <c r="I19" t="n">
         <v>530.777798425697</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.15</v>
+        <v>-3.99</v>
       </c>
       <c r="L19" t="n">
         <v>4.24</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.69</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43654</v>
+        <v>43655</v>
       </c>
       <c r="H20" t="n">
-        <v>602.4</v>
+        <v>594.8</v>
       </c>
       <c r="I20" t="n">
         <v>597.5637254310474</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K20" t="n">
-        <v>12.62</v>
+        <v>11.2</v>
       </c>
       <c r="L20" t="n">
         <v>3.25</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.32</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H21" t="n">
-        <v>550.5</v>
+        <v>599.8</v>
       </c>
       <c r="I21" t="n">
         <v>570.9178800445476</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K21" t="n">
-        <v>7.45</v>
+        <v>-0.84</v>
       </c>
       <c r="L21" t="n">
         <v>2.08</v>
@@ -1638,7 +1889,7 @@
         <v>1.48</v>
       </c>
       <c r="N21" t="n">
-        <v>4.31</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O21" t="n">
         <v>-1.26</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.93</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43854</v>
+        <v>43857</v>
       </c>
       <c r="H22" t="n">
-        <v>622.3</v>
+        <v>606.6</v>
       </c>
       <c r="I22" t="n">
         <v>620.3640949836746</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>1.13</v>
       </c>
       <c r="L22" t="n">
         <v>7.85</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>6.01</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43950</v>
+        <v>43951</v>
       </c>
       <c r="H23" t="n">
-        <v>488.6</v>
+        <v>500.9</v>
       </c>
       <c r="I23" t="n">
         <v>498.3369270357366</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K23" t="n">
-        <v>19.45</v>
+        <v>17.42</v>
       </c>
       <c r="L23" t="n">
         <v>3.86</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>14.32</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43966</v>
+        <v>43969</v>
       </c>
       <c r="H24" t="n">
-        <v>444.1</v>
+        <v>418.3</v>
       </c>
       <c r="I24" t="n">
         <v>429.1654510798054</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K24" t="n">
-        <v>-11.34</v>
+        <v>-16.49</v>
       </c>
       <c r="L24" t="n">
-        <v>13.04</v>
+        <v>17.03</v>
       </c>
       <c r="M24" t="n">
         <v>4.41</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>18.46</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H25" t="n">
-        <v>475.8</v>
+        <v>493.8</v>
       </c>
       <c r="I25" t="n">
         <v>487.4018552716982</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>-13.75</v>
+        <v>-18.05</v>
       </c>
       <c r="L25" t="n">
-        <v>14.15</v>
+        <v>18.93</v>
       </c>
       <c r="M25" t="n">
         <v>2.89</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.33</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44042</v>
+        <v>44043</v>
       </c>
       <c r="H26" t="n">
-        <v>525.3</v>
+        <v>516.4</v>
       </c>
       <c r="I26" t="n">
         <v>521.9954736017086</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K26" t="n">
-        <v>6.38</v>
+        <v>4.58</v>
       </c>
       <c r="L26" t="n">
         <v>6.03</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>10.53</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44064</v>
+        <v>44067</v>
       </c>
       <c r="H27" t="n">
-        <v>542.8</v>
+        <v>558.5</v>
       </c>
       <c r="I27" t="n">
         <v>557.2211276956396</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.11</v>
+        <v>-8.15</v>
       </c>
       <c r="L27" t="n">
-        <v>5.42</v>
+        <v>8.73</v>
       </c>
       <c r="M27" t="n">
         <v>1.22</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>8.98</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44092</v>
+        <v>44095</v>
       </c>
       <c r="H28" t="n">
-        <v>528.6</v>
+        <v>524.6</v>
       </c>
       <c r="I28" t="n">
         <v>526.5874104184553</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.35</v>
+        <v>-6.07</v>
       </c>
       <c r="L28" t="n">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
       <c r="M28" t="n">
         <v>1.84</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44109</v>
+        <v>44110</v>
       </c>
       <c r="H29" t="n">
-        <v>557.2</v>
+        <v>572</v>
       </c>
       <c r="I29" t="n">
         <v>557.922575016901</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.21</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>7.89</v>
+        <v>9.42</v>
       </c>
       <c r="M29" t="n">
         <v>1.9</v>
       </c>
       <c r="N29" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="O29" t="n">
         <v>-0.76</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,25 +2489,25 @@
         <v>7.69</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44223</v>
+        <v>44224</v>
       </c>
       <c r="H30" t="n">
-        <v>704.8</v>
+        <v>685.7</v>
       </c>
       <c r="I30" t="n">
         <v>701.0419017428529</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K30" t="n">
-        <v>23.22</v>
+        <v>19.88</v>
       </c>
       <c r="L30" t="n">
         <v>1.56</v>
       </c>
       <c r="M30" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="N30" t="n">
         <v>3.64</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>8.32</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44228</v>
+        <v>44229</v>
       </c>
       <c r="H31" t="n">
-        <v>738.4</v>
+        <v>780.3</v>
       </c>
       <c r="I31" t="n">
         <v>742.7192579398627</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>-7.69</v>
+        <v>-13.8</v>
       </c>
       <c r="L31" t="n">
-        <v>8.09</v>
+        <v>15.09</v>
       </c>
       <c r="M31" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="N31" t="n">
         <v>6.21</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>11.01</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44271</v>
+        <v>44272</v>
       </c>
       <c r="H32" t="n">
-        <v>756.1</v>
+        <v>747.7</v>
       </c>
       <c r="I32" t="n">
         <v>748.1164856641924</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.1</v>
+        <v>-4.18</v>
       </c>
       <c r="L32" t="n">
-        <v>4.05</v>
+        <v>4.51</v>
       </c>
       <c r="M32" t="n">
         <v>2.41</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.93</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44336</v>
+        <v>44337</v>
       </c>
       <c r="H33" t="n">
-        <v>716.4</v>
+        <v>748.6</v>
       </c>
       <c r="I33" t="n">
         <v>743.2833692264743</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K33" t="n">
-        <v>4.19</v>
+        <v>-0.12</v>
       </c>
       <c r="L33" t="n">
         <v>4.49</v>
@@ -2322,7 +2717,7 @@
         <v>2.09</v>
       </c>
       <c r="N33" t="n">
-        <v>4.18</v>
+        <v>4.49</v>
       </c>
       <c r="O33" t="n">
         <v>-1.11</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>9.35</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44396</v>
+        <v>44397</v>
       </c>
       <c r="H34" t="n">
-        <v>735.5</v>
+        <v>721.6</v>
       </c>
       <c r="I34" t="n">
         <v>733.4092033164833</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.75</v>
+        <v>-3.61</v>
       </c>
       <c r="L34" t="n">
-        <v>3.62</v>
+        <v>4.07</v>
       </c>
       <c r="M34" t="n">
         <v>2.33</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>5.54</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44413</v>
+        <v>44414</v>
       </c>
       <c r="H35" t="n">
-        <v>742.4</v>
+        <v>746.3</v>
       </c>
       <c r="I35" t="n">
         <v>746.0328556667844</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.88</v>
+        <v>-3.42</v>
       </c>
       <c r="L35" t="n">
         <v>4.42</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.98</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44496</v>
+        <v>44497</v>
       </c>
       <c r="H36" t="n">
-        <v>821.4</v>
+        <v>796.8</v>
       </c>
       <c r="I36" t="n">
         <v>799.2084560806095</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K36" t="n">
-        <v>10.06</v>
+        <v>6.77</v>
       </c>
       <c r="L36" t="n">
         <v>1.25</v>
@@ -2493,7 +2924,7 @@
         <v>1.78</v>
       </c>
       <c r="N36" t="n">
-        <v>1.42</v>
+        <v>2.99</v>
       </c>
       <c r="O36" t="n">
         <v>0.53</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.56</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44564</v>
+        <v>44565</v>
       </c>
       <c r="H37" t="n">
-        <v>759.8</v>
+        <v>764.3</v>
       </c>
       <c r="I37" t="n">
         <v>762.1979121352779</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K37" t="n">
-        <v>4.64</v>
+        <v>4.08</v>
       </c>
       <c r="L37" t="n">
         <v>3.54</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>5.85</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44586</v>
+        <v>44588</v>
       </c>
       <c r="H38" t="n">
-        <v>744</v>
+        <v>737.5</v>
       </c>
       <c r="I38" t="n">
         <v>740.1907933612606</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.66</v>
+        <v>-3.51</v>
       </c>
       <c r="L38" t="n">
-        <v>5.53</v>
+        <v>6.12</v>
       </c>
       <c r="M38" t="n">
-        <v>1.88</v>
+        <v>2.55</v>
       </c>
       <c r="N38" t="n">
         <v>2.3</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>6.44</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H39" t="n">
-        <v>724.1</v>
+        <v>740</v>
       </c>
       <c r="I39" t="n">
         <v>724.7005314387297</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K39" t="n">
-        <v>1.82</v>
+        <v>-0.34</v>
       </c>
       <c r="L39" t="n">
         <v>4.41</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44663</v>
+        <v>44664</v>
       </c>
       <c r="H40" t="n">
-        <v>746.8</v>
+        <v>732.5</v>
       </c>
       <c r="I40" t="n">
         <v>738.4811792511288</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K40" t="n">
-        <v>0.92</v>
+        <v>-1.01</v>
       </c>
       <c r="L40" t="n">
         <v>5.3</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>10.62</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44707</v>
+        <v>44708</v>
       </c>
       <c r="H41" t="n">
-        <v>683.4</v>
+        <v>696</v>
       </c>
       <c r="I41" t="n">
         <v>694.8005214723574</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K41" t="n">
-        <v>6.7</v>
+        <v>4.98</v>
       </c>
       <c r="L41" t="n">
         <v>2.55</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>7.63</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44725</v>
+        <v>44726</v>
       </c>
       <c r="H42" t="n">
-        <v>663.3</v>
+        <v>656</v>
       </c>
       <c r="I42" t="n">
         <v>656.763721411388</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.7</v>
+        <v>-5.75</v>
       </c>
       <c r="L42" t="n">
-        <v>6.01</v>
+        <v>6.25</v>
       </c>
       <c r="M42" t="n">
         <v>2.04</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>6.8</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44748</v>
+        <v>44749</v>
       </c>
       <c r="H43" t="n">
-        <v>685.6</v>
+        <v>697.9</v>
       </c>
       <c r="I43" t="n">
         <v>685.8679513018013</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.51</v>
+        <v>-6.39</v>
       </c>
       <c r="L43" t="n">
-        <v>5.14</v>
+        <v>6.55</v>
       </c>
       <c r="M43" t="n">
         <v>1.2</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>6.21</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44799</v>
+        <v>44802</v>
       </c>
       <c r="H44" t="n">
-        <v>732.6</v>
+        <v>719.7</v>
       </c>
       <c r="I44" t="n">
         <v>719.9039385180458</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K44" t="n">
-        <v>4.97</v>
+        <v>3.12</v>
       </c>
       <c r="L44" t="n">
         <v>4.21</v>
       </c>
       <c r="M44" t="n">
-        <v>1.17</v>
+        <v>1.92</v>
       </c>
       <c r="N44" t="n">
         <v>2.44</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>4.89</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44816</v>
+        <v>44817</v>
       </c>
       <c r="H45" t="n">
-        <v>746.8</v>
+        <v>756.6</v>
       </c>
       <c r="I45" t="n">
         <v>754.879048569028</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.77</v>
+        <v>-5.13</v>
       </c>
       <c r="L45" t="n">
-        <v>4.84</v>
+        <v>5.32</v>
       </c>
       <c r="M45" t="n">
         <v>0.51</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>4.78</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H46" t="n">
-        <v>743</v>
+        <v>723.1</v>
       </c>
       <c r="I46" t="n">
         <v>725.7458132964027</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.8</v>
+        <v>-4.43</v>
       </c>
       <c r="L46" t="n">
-        <v>2.19</v>
+        <v>5.04</v>
       </c>
       <c r="M46" t="n">
         <v>1.27</v>
       </c>
       <c r="N46" t="n">
-        <v>2.13</v>
+        <v>2.68</v>
       </c>
       <c r="O46" t="n">
         <v>1.31</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>6.64</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44862</v>
+        <v>44865</v>
       </c>
       <c r="H47" t="n">
-        <v>729.4</v>
+        <v>748.4</v>
       </c>
       <c r="I47" t="n">
         <v>737.9093009996595</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.87</v>
+        <v>-3.5</v>
       </c>
       <c r="L47" t="n">
-        <v>2.16</v>
+        <v>3.58</v>
       </c>
       <c r="M47" t="n">
         <v>1.68</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.35</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44931</v>
+        <v>44932</v>
       </c>
       <c r="H48" t="n">
-        <v>799.8</v>
+        <v>797.2</v>
       </c>
       <c r="I48" t="n">
         <v>798.2371119262972</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K48" t="n">
-        <v>6.87</v>
+        <v>6.52</v>
       </c>
       <c r="L48" t="n">
         <v>1.98</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>5.01</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44946</v>
+        <v>44949</v>
       </c>
       <c r="H49" t="n">
-        <v>830.5</v>
+        <v>836.6</v>
       </c>
       <c r="I49" t="n">
         <v>831.9495633794385</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.18</v>
+        <v>-4.94</v>
       </c>
       <c r="L49" t="n">
-        <v>4.68</v>
+        <v>5.53</v>
       </c>
       <c r="M49" t="n">
         <v>0.9</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.08</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44956</v>
+        <v>44957</v>
       </c>
       <c r="H50" t="n">
-        <v>807.1</v>
+        <v>801.8</v>
       </c>
       <c r="I50" t="n">
         <v>802.2942591240015</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.53</v>
+        <v>-4.16</v>
       </c>
       <c r="L50" t="n">
         <v>5.45</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>6.59</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45019</v>
+        <v>45021</v>
       </c>
       <c r="H51" t="n">
-        <v>805.3</v>
+        <v>826.9</v>
       </c>
       <c r="I51" t="n">
         <v>817.24505037778</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.44</v>
+        <v>-3.13</v>
       </c>
       <c r="L51" t="n">
         <v>4.89</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>5.93</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45050</v>
+        <v>45051</v>
       </c>
       <c r="H52" t="n">
-        <v>863.9</v>
+        <v>812.8</v>
       </c>
       <c r="I52" t="n">
         <v>819.4657749101743</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K52" t="n">
-        <v>4.47</v>
+        <v>-1.71</v>
       </c>
       <c r="L52" t="n">
         <v>2.29</v>
       </c>
       <c r="M52" t="n">
-        <v>0.35</v>
+        <v>5.14</v>
       </c>
       <c r="N52" t="n">
-        <v>1.52</v>
+        <v>5.92</v>
       </c>
       <c r="O52" t="n">
         <v>2.68</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.91</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45103</v>
+        <v>45104</v>
       </c>
       <c r="H53" t="n">
-        <v>817.8</v>
+        <v>829.3</v>
       </c>
       <c r="I53" t="n">
         <v>825.640482666239</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.62</v>
+        <v>-2.03</v>
       </c>
       <c r="L53" t="n">
         <v>3.84</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>4.36</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45117</v>
+        <v>45118</v>
       </c>
       <c r="H54" t="n">
-        <v>828.2</v>
+        <v>824.2</v>
       </c>
       <c r="I54" t="n">
         <v>826.1745763219967</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.13</v>
+        <v>-0.61</v>
       </c>
       <c r="L54" t="n">
         <v>1.21</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>6.08</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45177</v>
+        <v>45180</v>
       </c>
       <c r="H55" t="n">
-        <v>811.7</v>
+        <v>815.9</v>
       </c>
       <c r="I55" t="n">
         <v>814.2416797535825</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K55" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="L55" t="n">
         <v>3.37</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>3.9</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45187</v>
+        <v>45189</v>
       </c>
       <c r="H56" t="n">
-        <v>814.5</v>
+        <v>781.8</v>
       </c>
       <c r="I56" t="n">
         <v>798.8454112840434</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.17</v>
+        <v>-4.18</v>
       </c>
       <c r="L56" t="n">
-        <v>0.48</v>
+        <v>4.38</v>
       </c>
       <c r="M56" t="n">
-        <v>0.48</v>
+        <v>1.84</v>
       </c>
       <c r="N56" t="n">
-        <v>1.97</v>
+        <v>4.01</v>
       </c>
       <c r="O56" t="n">
         <v>0.52</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>6.19</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="H57" t="n">
-        <v>764.3</v>
+        <v>779.6</v>
       </c>
       <c r="I57" t="n">
         <v>770.7448329219145</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K57" t="n">
-        <v>2.24</v>
+        <v>0.28</v>
       </c>
       <c r="L57" t="n">
         <v>2.26</v>
@@ -3690,7 +4373,7 @@
         <v>1.71</v>
       </c>
       <c r="N57" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="O57" t="n">
         <v>-4.01</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>4.19</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45302</v>
+        <v>45303</v>
       </c>
       <c r="H58" t="n">
-        <v>824.5</v>
+        <v>820.6</v>
       </c>
       <c r="I58" t="n">
         <v>822.069634449037</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K58" t="n">
-        <v>5.76</v>
+        <v>5.26</v>
       </c>
       <c r="L58" t="n">
         <v>1.68</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>4.5</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="H59" t="n">
-        <v>735.2</v>
+        <v>740.1</v>
       </c>
       <c r="I59" t="n">
         <v>735.8481753755966</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K59" t="n">
-        <v>10.41</v>
+        <v>9.81</v>
       </c>
       <c r="L59" t="n">
         <v>2.58</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>4.67</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H60" t="n">
-        <v>741.3</v>
+        <v>723.8</v>
       </c>
       <c r="I60" t="n">
         <v>738.6551441223149</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K60" t="n">
-        <v>0.16</v>
+        <v>-2.2</v>
       </c>
       <c r="L60" t="n">
-        <v>1.15</v>
+        <v>2.36</v>
       </c>
       <c r="M60" t="n">
         <v>1.41</v>
       </c>
       <c r="N60" t="n">
-        <v>1.59</v>
+        <v>2.36</v>
       </c>
       <c r="O60" t="n">
         <v>0.67</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>6.71</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c r="H61" t="n">
-        <v>758.6</v>
+        <v>763.8</v>
       </c>
       <c r="I61" t="n">
         <v>758.8986176013983</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K61" t="n">
-        <v>-4.81</v>
+        <v>-5.53</v>
       </c>
       <c r="L61" t="n">
-        <v>5</v>
+        <v>6.73</v>
       </c>
       <c r="M61" t="n">
         <v>0.53</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>4.64</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H62" t="n">
-        <v>786.1</v>
+        <v>741.6</v>
       </c>
       <c r="I62" t="n">
         <v>744.4675181813484</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K62" t="n">
-        <v>2.92</v>
+        <v>-2.91</v>
       </c>
       <c r="L62" t="n">
-        <v>1.96</v>
+        <v>4.82</v>
       </c>
       <c r="M62" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="N62" t="n">
-        <v>1.44</v>
+        <v>5.66</v>
       </c>
       <c r="O62" t="n">
         <v>0.6899999999999999</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>9.15</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45461</v>
+        <v>45462</v>
       </c>
       <c r="H63" t="n">
-        <v>803.9</v>
+        <v>828.9</v>
       </c>
       <c r="I63" t="n">
         <v>809.4842336367865</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K63" t="n">
-        <v>-8.4</v>
+        <v>-11.77</v>
       </c>
       <c r="L63" t="n">
-        <v>8.58</v>
+        <v>12.59</v>
       </c>
       <c r="M63" t="n">
         <v>0.84</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>7.29</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45477</v>
+        <v>45478</v>
       </c>
       <c r="H64" t="n">
-        <v>863.6</v>
+        <v>824</v>
       </c>
       <c r="I64" t="n">
         <v>838.2758305304052</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K64" t="n">
-        <v>4.19</v>
+        <v>-0.59</v>
       </c>
       <c r="L64" t="n">
         <v>3.25</v>
       </c>
       <c r="M64" t="n">
-        <v>1.13</v>
+        <v>2.44</v>
       </c>
       <c r="N64" t="n">
-        <v>2.34</v>
+        <v>4.59</v>
       </c>
       <c r="O64" t="n">
         <v>3.11</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>8.26</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45553</v>
+        <v>45554</v>
       </c>
       <c r="H65" t="n">
-        <v>847.4</v>
+        <v>854.2</v>
       </c>
       <c r="I65" t="n">
         <v>848.8726904072601</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.84</v>
+        <v>-3.67</v>
       </c>
       <c r="L65" t="n">
-        <v>3.08</v>
+        <v>4.31</v>
       </c>
       <c r="M65" t="n">
         <v>1.28</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>3.43</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H66" t="n">
-        <v>863.1</v>
+        <v>841</v>
       </c>
       <c r="I66" t="n">
         <v>854.8684349162006</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K66" t="n">
-        <v>1.04</v>
+        <v>-1.55</v>
       </c>
       <c r="L66" t="n">
-        <v>0.54</v>
+        <v>2.05</v>
       </c>
       <c r="M66" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="N66" t="n">
-        <v>1.73</v>
+        <v>2.56</v>
       </c>
       <c r="O66" t="n">
         <v>0.8</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>5.86</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45583</v>
+        <v>45586</v>
       </c>
       <c r="H67" t="n">
-        <v>840.9</v>
+        <v>864.4</v>
       </c>
       <c r="I67" t="n">
         <v>862.6694709796994</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K67" t="n">
-        <v>0.01</v>
+        <v>-2.78</v>
       </c>
       <c r="L67" t="n">
-        <v>2.63</v>
+        <v>3.94</v>
       </c>
       <c r="M67" t="n">
-        <v>0.75</v>
+        <v>1.97</v>
       </c>
       <c r="N67" t="n">
-        <v>2.24</v>
+        <v>2.79</v>
       </c>
       <c r="O67" t="n">
         <v>-2.56</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>5.94</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H68" t="n">
-        <v>896.8</v>
+        <v>885.8</v>
       </c>
       <c r="I68" t="n">
         <v>885.8280310651555</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K68" t="n">
-        <v>3.75</v>
+        <v>2.48</v>
       </c>
       <c r="L68" t="n">
         <v>3.29</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>5.85</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45692</v>
+        <v>45693</v>
       </c>
       <c r="H69" t="n">
-        <v>860.4</v>
+        <v>868.9</v>
       </c>
       <c r="I69" t="n">
         <v>862.4732409089452</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K69" t="n">
-        <v>2.87</v>
+        <v>1.91</v>
       </c>
       <c r="L69" t="n">
         <v>2.45</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>5.69</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45894</v>
+        <v>45895</v>
       </c>
       <c r="H70" t="n">
-        <v>982</v>
+        <v>973.4</v>
       </c>
       <c r="I70" t="n">
         <v>974.7005860005628</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K70" t="n">
-        <v>13.02</v>
+        <v>12.03</v>
       </c>
       <c r="L70" t="n">
         <v>4.41</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>7</v>
+      </c>
+      <c r="U70" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>4.27</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="H71" t="n">
-        <v>973.45</v>
+        <v>982.5</v>
       </c>
       <c r="I71" t="n">
         <v>981.0099126924413</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.01</v>
+        <v>-0.93</v>
       </c>
       <c r="L71" t="n">
-        <v>1.26</v>
+        <v>1.69</v>
       </c>
       <c r="M71" t="n">
         <v>0.91</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,25 +5387,25 @@
         <v>4.57</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="H72" t="n">
-        <v>977.5</v>
+        <v>962.2</v>
       </c>
       <c r="I72" t="n">
         <v>970.4625591061579</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.51</v>
+        <v>-2.07</v>
       </c>
       <c r="L72" t="n">
-        <v>1.58</v>
+        <v>2.7</v>
       </c>
       <c r="M72" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="N72" t="n">
         <v>2.41</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>4</v>
+      </c>
+      <c r="U72" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>4.27</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="H73" t="n">
-        <v>784.9</v>
+        <v>787.1</v>
       </c>
       <c r="I73" t="n">
         <v>785.2633305986749</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K73" t="n">
-        <v>18.43</v>
+        <v>18.2</v>
       </c>
       <c r="L73" t="n">
         <v>3.3</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>6</v>
+      </c>
+      <c r="U73" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>6.08</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="H74" t="n">
-        <v>819.6</v>
+        <v>777.6</v>
       </c>
       <c r="I74" t="n">
         <v>786.151054551053</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K74" t="n">
-        <v>4.13</v>
+        <v>-1.21</v>
       </c>
       <c r="L74" t="n">
         <v>1.85</v>
       </c>
       <c r="M74" t="n">
-        <v>1.29</v>
+        <v>3.61</v>
       </c>
       <c r="N74" t="n">
-        <v>2.4</v>
+        <v>5.12</v>
       </c>
       <c r="O74" t="n">
         <v>0.28</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>7.44</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="H75" t="n">
-        <v>713</v>
+        <v>731</v>
       </c>
       <c r="I75" t="n">
         <v>724.9066524236027</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K75" t="n">
-        <v>8.31</v>
+        <v>5.99</v>
       </c>
       <c r="L75" t="n">
         <v>1.59</v>
@@ -4716,7 +5615,7 @@
         <v>2</v>
       </c>
       <c r="N75" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="O75" t="n">
         <v>-5.12</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>6.73</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H76" t="n">
-        <v>702.75</v>
+        <v>692.25</v>
       </c>
       <c r="I76" t="n">
         <v>702.4560109414134</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K76" t="n">
-        <v>-3.86</v>
+        <v>-5.3</v>
       </c>
       <c r="L76" t="n">
-        <v>4.1</v>
+        <v>5.54</v>
       </c>
       <c r="M76" t="n">
         <v>1.66</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4833,6 +5756,14 @@
       <c r="Q77" t="n">
         <v>14</v>
       </c>
+      <c r="R77" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9791,7 +10722,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.5</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="6">
@@ -9801,7 +10732,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -9811,7 +10742,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8">
@@ -9821,7 +10752,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -9831,7 +10762,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -9841,7 +10772,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11">
@@ -9851,7 +10782,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -9861,7 +10792,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -9871,7 +10802,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>38.7</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="14">
@@ -9881,7 +10812,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.39</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="15">
@@ -9891,7 +10822,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.19</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="16">
@@ -9901,7 +10832,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.54</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="17">
@@ -9911,7 +10842,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>45.25</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="18">
@@ -9921,7 +10852,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.7</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="19">
@@ -9931,7 +10862,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.82</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="20">
@@ -9941,7 +10872,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.44</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="21">
@@ -9951,7 +10882,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.15</v>
+        <v>18.93</v>
       </c>
     </row>
     <row r="22">
@@ -9961,7 +10892,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -9971,7 +10902,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -9981,7 +10912,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="25">
@@ -10001,7 +10932,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.87</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="27">
@@ -10021,7 +10952,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
